--- a/data/winchance.xlsx
+++ b/data/winchance.xlsx
@@ -1154,7 +1154,7 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -2707,7 +2707,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="3">
-        <v>0.3339030068370312</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="168">
@@ -2715,7 +2715,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="3">
-        <v>0.24050826052401905</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="169">
@@ -2723,7 +2723,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="3">
-        <v>0.07997229321540789</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="170">
@@ -2731,7 +2731,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="3">
-        <v>0.15531204271756133</v>
+        <v>15.53</v>
       </c>
     </row>
     <row r="171">
@@ -2739,7 +2739,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="3">
-        <v>0.05084575301730306</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="172">
@@ -2747,7 +2747,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="3">
-        <v>0.0432652948982217</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="173">
@@ -2755,7 +2755,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="3">
-        <v>0.03300328144820577</v>
+        <v>3.3000000000000003</v>
       </c>
     </row>
     <row r="174">
@@ -2763,7 +2763,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="3">
-        <v>0.03033826054432165</v>
+        <v>3.0300000000000002</v>
       </c>
     </row>
     <row r="175">
@@ -2771,7 +2771,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="3">
-        <v>0.02527723750561296</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="176">
@@ -2779,7 +2779,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="3">
-        <v>0.005233510459575083</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="177">
@@ -2787,7 +2787,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="3">
-        <v>0.0023410588327399794</v>
+        <v>0.22999999999999998</v>
       </c>
     </row>
     <row r="178">

--- a/data/winchance.xlsx
+++ b/data/winchance.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="365">
   <si>
     <t>Saint Louis Billikens</t>
   </si>
@@ -973,48 +973,48 @@
     <t>St. Thomas-Minnesota Tommies</t>
   </si>
   <si>
+    <t>App State Mountaineers</t>
+  </si>
+  <si>
     <t>Arkansas State Red Wolves</t>
   </si>
   <si>
+    <t>Coastal Carolina Chanticleers</t>
+  </si>
+  <si>
+    <t>Georgia Southern Eagles</t>
+  </si>
+  <si>
+    <t>Georgia State Panthers</t>
+  </si>
+  <si>
+    <t>James Madison Dukes</t>
+  </si>
+  <si>
+    <t>Louisiana Ragin' Cajuns</t>
+  </si>
+  <si>
+    <t>Marshall Thundering Herd</t>
+  </si>
+  <si>
+    <t>Old Dominion Monarchs</t>
+  </si>
+  <si>
+    <t>South Alabama Jaguars</t>
+  </si>
+  <si>
+    <t>Southern Miss Golden Eagles</t>
+  </si>
+  <si>
     <t>Texas State Bobcats</t>
   </si>
   <si>
-    <t>App State Mountaineers</t>
-  </si>
-  <si>
-    <t>Coastal Carolina Chanticleers</t>
-  </si>
-  <si>
-    <t>South Alabama Jaguars</t>
-  </si>
-  <si>
-    <t>James Madison Dukes</t>
-  </si>
-  <si>
-    <t>Southern Miss Golden Eagles</t>
-  </si>
-  <si>
-    <t>Marshall Thundering Herd</t>
-  </si>
-  <si>
-    <t>Georgia Southern Eagles</t>
-  </si>
-  <si>
-    <t>Old Dominion Monarchs</t>
-  </si>
-  <si>
-    <t>South Dakota State Jackrabbits</t>
-  </si>
-  <si>
-    <t>Louisiana Ragin' Cajuns</t>
-  </si>
-  <si>
-    <t>Georgia State Panthers</t>
-  </si>
-  <si>
     <t>Troy Trojans</t>
   </si>
   <si>
+    <t>UL Monroe Warhawks</t>
+  </si>
+  <si>
     <t>Bethune-Cookman Wildcats</t>
   </si>
   <si>
@@ -1040,9 +1040,6 @@
   </si>
   <si>
     <t>Alcorn State Braves</t>
-  </si>
-  <si>
-    <t>UL Monroe Warhawks</t>
   </si>
   <si>
     <t>Mississippi Valley State Delta Devils</t>
@@ -1115,8 +1112,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -1144,7 +1142,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1155,6 +1153,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -3930,112 +3931,112 @@
       <c r="A320" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B320" s="2" t="s">
-        <v>1</v>
+      <c r="B320" s="4">
+        <v>12.28012081410357</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B321" s="2" t="s">
-        <v>1</v>
+      <c r="B321" s="4">
+        <v>9.485409227229336</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B322" s="2" t="s">
-        <v>1</v>
+      <c r="B322" s="4">
+        <v>14.168378450405877</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B323" s="2" t="s">
-        <v>1</v>
+      <c r="B323" s="4">
+        <v>0.5125845143883176</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B324" s="2" t="s">
-        <v>1</v>
+      <c r="B324" s="4">
+        <v>0.03644989804179915</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B325" s="2" t="s">
-        <v>1</v>
+      <c r="B325" s="4">
+        <v>1.9597979467004172</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B326" s="2" t="s">
-        <v>1</v>
+      <c r="B326" s="4">
+        <v>0.10372450796720344</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B327" s="2" t="s">
-        <v>1</v>
+      <c r="B327" s="4">
+        <v>18.56310220344689</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B328" s="2" t="s">
-        <v>1</v>
+      <c r="B328" s="4">
+        <v>0.42512088214230054</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B329" s="2" t="s">
-        <v>1</v>
+      <c r="B329" s="4">
+        <v>7.174404538956834</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B330" s="2" t="s">
-        <v>1</v>
+      <c r="B330" s="4">
+        <v>2.127917232997722</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B331" s="2" t="s">
-        <v>1</v>
+      <c r="B331" s="4">
+        <v>7.0228275051137175</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B332" s="2" t="s">
-        <v>1</v>
+      <c r="B332" s="4">
+        <v>26.139556557297244</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B333" s="2" t="s">
-        <v>1</v>
+      <c r="B333" s="4">
+        <v>6.057212087675254E-4</v>
       </c>
     </row>
     <row r="334">
@@ -4112,7 +4113,7 @@
     </row>
     <row r="343">
       <c r="A343" s="1" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>1</v>
@@ -4120,7 +4121,7 @@
     </row>
     <row r="344">
       <c r="A344" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>1</v>
@@ -4128,7 +4129,7 @@
     </row>
     <row r="345">
       <c r="A345" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>1</v>
@@ -4136,7 +4137,7 @@
     </row>
     <row r="346">
       <c r="A346" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>1</v>
@@ -4144,7 +4145,7 @@
     </row>
     <row r="347">
       <c r="A347" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>1</v>
@@ -4152,7 +4153,7 @@
     </row>
     <row r="348">
       <c r="A348" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>1</v>
@@ -4160,7 +4161,7 @@
     </row>
     <row r="349">
       <c r="A349" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>1</v>
@@ -4168,7 +4169,7 @@
     </row>
     <row r="350">
       <c r="A350" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>1</v>
@@ -4176,7 +4177,7 @@
     </row>
     <row r="351">
       <c r="A351" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>1</v>
@@ -4184,7 +4185,7 @@
     </row>
     <row r="352">
       <c r="A352" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>1</v>
@@ -4192,7 +4193,7 @@
     </row>
     <row r="353">
       <c r="A353" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>1</v>
@@ -4200,7 +4201,7 @@
     </row>
     <row r="354">
       <c r="A354" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>1</v>
@@ -4208,7 +4209,7 @@
     </row>
     <row r="355">
       <c r="A355" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>1</v>
@@ -4216,7 +4217,7 @@
     </row>
     <row r="356">
       <c r="A356" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>1</v>
@@ -4224,7 +4225,7 @@
     </row>
     <row r="357">
       <c r="A357" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>1</v>
@@ -4232,7 +4233,7 @@
     </row>
     <row r="358">
       <c r="A358" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>1</v>
@@ -4240,7 +4241,7 @@
     </row>
     <row r="359">
       <c r="A359" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>1</v>
@@ -4248,7 +4249,7 @@
     </row>
     <row r="360">
       <c r="A360" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>1</v>
@@ -4256,7 +4257,7 @@
     </row>
     <row r="361">
       <c r="A361" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>1</v>
@@ -4264,7 +4265,7 @@
     </row>
     <row r="362">
       <c r="A362" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>1</v>
@@ -4272,7 +4273,7 @@
     </row>
     <row r="363">
       <c r="A363" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>1</v>
@@ -4280,7 +4281,7 @@
     </row>
     <row r="364">
       <c r="A364" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>1</v>
@@ -4288,7 +4289,7 @@
     </row>
     <row r="365">
       <c r="A365" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>1</v>

--- a/data/winchance.xlsx
+++ b/data/winchance.xlsx
@@ -1142,7 +1142,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1157,6 +1157,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3963,8 +3966,8 @@
       <c r="A324" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B324" s="4">
-        <v>0.03644989804179915</v>
+      <c r="B324" s="5">
+        <v>0.1</v>
       </c>
     </row>
     <row r="325">
@@ -4035,8 +4038,8 @@
       <c r="A333" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B333" s="4">
-        <v>6.057212087675254E-4</v>
+      <c r="B333" s="5">
+        <v>0.1</v>
       </c>
     </row>
     <row r="334">

--- a/data/winchance.xlsx
+++ b/data/winchance.xlsx
@@ -1116,7 +1116,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1126,6 +1126,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1142,7 +1147,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1154,6 +1159,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -2713,14 +2721,16 @@
       <c r="B167" s="3">
         <v>33.39</v>
       </c>
+      <c r="C167" s="4"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="s">
         <v>168</v>
       </c>
       <c r="B168" s="3">
-        <v>24.05</v>
-      </c>
+        <v>23.62</v>
+      </c>
+      <c r="C168" s="4"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="s">
@@ -2729,6 +2739,7 @@
       <c r="B169" s="3">
         <v>8.0</v>
       </c>
+      <c r="C169" s="4"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="s">
@@ -2737,14 +2748,16 @@
       <c r="B170" s="3">
         <v>15.53</v>
       </c>
+      <c r="C170" s="4"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="s">
         <v>171</v>
       </c>
       <c r="B171" s="3">
-        <v>5.08</v>
-      </c>
+        <v>5.09</v>
+      </c>
+      <c r="C171" s="4"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="s">
@@ -2753,6 +2766,7 @@
       <c r="B172" s="3">
         <v>4.33</v>
       </c>
+      <c r="C172" s="4"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="s">
@@ -2761,6 +2775,7 @@
       <c r="B173" s="3">
         <v>3.3000000000000003</v>
       </c>
+      <c r="C173" s="4"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="s">
@@ -2769,6 +2784,7 @@
       <c r="B174" s="3">
         <v>3.0300000000000002</v>
       </c>
+      <c r="C174" s="4"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="s">
@@ -2777,22 +2793,25 @@
       <c r="B175" s="3">
         <v>2.53</v>
       </c>
+      <c r="C175" s="4"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="s">
         <v>176</v>
       </c>
       <c r="B176" s="3">
-        <v>0.52</v>
-      </c>
+        <v>1.17</v>
+      </c>
+      <c r="C176" s="4"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="s">
         <v>177</v>
       </c>
       <c r="B177" s="3">
-        <v>0.22999999999999998</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="C177" s="4"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="s">
@@ -3934,7 +3953,7 @@
       <c r="A320" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B320" s="4">
+      <c r="B320" s="5">
         <v>12.28012081410357</v>
       </c>
     </row>
@@ -3942,7 +3961,7 @@
       <c r="A321" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B321" s="4">
+      <c r="B321" s="5">
         <v>9.485409227229336</v>
       </c>
     </row>
@@ -3950,7 +3969,7 @@
       <c r="A322" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B322" s="4">
+      <c r="B322" s="5">
         <v>14.168378450405877</v>
       </c>
     </row>
@@ -3958,7 +3977,7 @@
       <c r="A323" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B323" s="4">
+      <c r="B323" s="5">
         <v>0.5125845143883176</v>
       </c>
     </row>
@@ -3966,7 +3985,7 @@
       <c r="A324" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B324" s="5">
+      <c r="B324" s="6">
         <v>0.1</v>
       </c>
     </row>
@@ -3974,7 +3993,7 @@
       <c r="A325" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B325" s="4">
+      <c r="B325" s="5">
         <v>1.9597979467004172</v>
       </c>
     </row>
@@ -3982,7 +4001,7 @@
       <c r="A326" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B326" s="4">
+      <c r="B326" s="5">
         <v>0.10372450796720344</v>
       </c>
     </row>
@@ -3990,7 +4009,7 @@
       <c r="A327" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B327" s="4">
+      <c r="B327" s="5">
         <v>18.56310220344689</v>
       </c>
     </row>
@@ -3998,7 +4017,7 @@
       <c r="A328" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B328" s="4">
+      <c r="B328" s="5">
         <v>0.42512088214230054</v>
       </c>
     </row>
@@ -4006,7 +4025,7 @@
       <c r="A329" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B329" s="4">
+      <c r="B329" s="5">
         <v>7.174404538956834</v>
       </c>
     </row>
@@ -4014,7 +4033,7 @@
       <c r="A330" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B330" s="4">
+      <c r="B330" s="5">
         <v>2.127917232997722</v>
       </c>
     </row>
@@ -4022,7 +4041,7 @@
       <c r="A331" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B331" s="4">
+      <c r="B331" s="5">
         <v>7.0228275051137175</v>
       </c>
     </row>
@@ -4030,7 +4049,7 @@
       <c r="A332" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B332" s="4">
+      <c r="B332" s="5">
         <v>26.139556557297244</v>
       </c>
     </row>
@@ -4038,7 +4057,7 @@
       <c r="A333" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B333" s="5">
+      <c r="B333" s="6">
         <v>0.1</v>
       </c>
     </row>

--- a/data/winchance.xlsx
+++ b/data/winchance.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="363">
   <si>
     <t>Saint Louis Billikens</t>
   </si>
@@ -802,16 +802,22 @@
     <t>UT Martin Skyhawks</t>
   </si>
   <si>
+    <t>Navy Midshipmen</t>
+  </si>
+  <si>
     <t>Boston University Terriers</t>
   </si>
   <si>
     <t>Colgate Raiders</t>
   </si>
   <si>
+    <t>Lehigh Mountain Hawks</t>
+  </si>
+  <si>
     <t>American University Eagles</t>
   </si>
   <si>
-    <t>Lehigh Mountain Hawks</t>
+    <t>Loyola Maryland Greyhounds</t>
   </si>
   <si>
     <t>Lafayette Leopards</t>
@@ -826,12 +832,6 @@
     <t>Bucknell Bison</t>
   </si>
   <si>
-    <t>Western Illinois Leathernecks</t>
-  </si>
-  <si>
-    <t>Florida Gators</t>
-  </si>
-  <si>
     <t>Alabama Crimson Tide</t>
   </si>
   <si>
@@ -850,9 +850,6 @@
     <t>Georgia Bulldogs</t>
   </si>
   <si>
-    <t>Navy Midshipmen</t>
-  </si>
-  <si>
     <t>Missouri Tigers</t>
   </si>
   <si>
@@ -872,9 +869,6 @@
   </si>
   <si>
     <t>South Carolina Gamecocks</t>
-  </si>
-  <si>
-    <t>Loyola Maryland Greyhounds</t>
   </si>
   <si>
     <t>Vanderbilt Commodores</t>
@@ -1147,7 +1141,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1162,6 +1156,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -3497,80 +3494,80 @@
       <c r="A263" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B263" s="2" t="s">
-        <v>1</v>
+      <c r="B263" s="5">
+        <v>56.23783103</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B264" s="2" t="s">
-        <v>1</v>
+      <c r="B264" s="5">
+        <v>11.15277519</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B265" s="2" t="s">
-        <v>1</v>
+      <c r="B265" s="5">
+        <v>8.851240114</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B266" s="2" t="s">
-        <v>1</v>
+      <c r="B266" s="5">
+        <v>8.743822284</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B267" s="2" t="s">
-        <v>1</v>
+      <c r="B267" s="5">
+        <v>5.277871477</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B268" s="2" t="s">
-        <v>1</v>
+      <c r="B268" s="5">
+        <v>4.535970317</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B269" s="2" t="s">
-        <v>1</v>
+      <c r="B269" s="5">
+        <v>2.521686364</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B270" s="2" t="s">
-        <v>1</v>
+      <c r="B270" s="5">
+        <v>1.019683406</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B271" s="2" t="s">
-        <v>1</v>
+      <c r="B271" s="5">
+        <v>0.8704373828</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B272" s="2" t="s">
-        <v>1</v>
+      <c r="B272" s="5">
+        <v>0.788682435</v>
       </c>
     </row>
     <row r="273">
@@ -3623,7 +3620,7 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>1</v>
@@ -3631,7 +3628,7 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>1</v>
@@ -3639,7 +3636,7 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>1</v>
@@ -3647,7 +3644,7 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>1</v>
@@ -3655,7 +3652,7 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>1</v>
@@ -3663,7 +3660,7 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>1</v>
@@ -3671,7 +3668,7 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>1</v>
@@ -3679,7 +3676,7 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>1</v>
@@ -3687,7 +3684,7 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>1</v>
@@ -3695,7 +3692,7 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>1</v>
@@ -3703,7 +3700,7 @@
     </row>
     <row r="289">
       <c r="A289" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>1</v>
@@ -3711,7 +3708,7 @@
     </row>
     <row r="290">
       <c r="A290" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>1</v>
@@ -3719,7 +3716,7 @@
     </row>
     <row r="291">
       <c r="A291" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>1</v>
@@ -3727,7 +3724,7 @@
     </row>
     <row r="292">
       <c r="A292" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>1</v>
@@ -3735,7 +3732,7 @@
     </row>
     <row r="293">
       <c r="A293" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>1</v>
@@ -3743,7 +3740,7 @@
     </row>
     <row r="294">
       <c r="A294" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>1</v>
@@ -3751,7 +3748,7 @@
     </row>
     <row r="295">
       <c r="A295" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>1</v>
@@ -3759,7 +3756,7 @@
     </row>
     <row r="296">
       <c r="A296" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>1</v>
@@ -3767,7 +3764,7 @@
     </row>
     <row r="297">
       <c r="A297" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>1</v>
@@ -3775,7 +3772,7 @@
     </row>
     <row r="298">
       <c r="A298" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>1</v>
@@ -3783,7 +3780,7 @@
     </row>
     <row r="299">
       <c r="A299" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>1</v>
@@ -3791,7 +3788,7 @@
     </row>
     <row r="300">
       <c r="A300" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>1</v>
@@ -3799,7 +3796,7 @@
     </row>
     <row r="301">
       <c r="A301" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>1</v>
@@ -3807,7 +3804,7 @@
     </row>
     <row r="302">
       <c r="A302" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>1</v>
@@ -3815,7 +3812,7 @@
     </row>
     <row r="303">
       <c r="A303" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>1</v>
@@ -3823,7 +3820,7 @@
     </row>
     <row r="304">
       <c r="A304" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>1</v>
@@ -3831,7 +3828,7 @@
     </row>
     <row r="305">
       <c r="A305" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>1</v>
@@ -3839,7 +3836,7 @@
     </row>
     <row r="306">
       <c r="A306" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>1</v>
@@ -3847,7 +3844,7 @@
     </row>
     <row r="307">
       <c r="A307" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>1</v>
@@ -3855,7 +3852,7 @@
     </row>
     <row r="308">
       <c r="A308" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>1</v>
@@ -3863,7 +3860,7 @@
     </row>
     <row r="309">
       <c r="A309" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>1</v>
@@ -3871,7 +3868,7 @@
     </row>
     <row r="310">
       <c r="A310" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>1</v>
@@ -3879,7 +3876,7 @@
     </row>
     <row r="311">
       <c r="A311" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>1</v>
@@ -3887,7 +3884,7 @@
     </row>
     <row r="312">
       <c r="A312" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>1</v>
@@ -3895,7 +3892,7 @@
     </row>
     <row r="313">
       <c r="A313" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>1</v>
@@ -3903,7 +3900,7 @@
     </row>
     <row r="314">
       <c r="A314" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>1</v>
@@ -3911,7 +3908,7 @@
     </row>
     <row r="315">
       <c r="A315" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>1</v>
@@ -3919,7 +3916,7 @@
     </row>
     <row r="316">
       <c r="A316" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>1</v>
@@ -3927,7 +3924,7 @@
     </row>
     <row r="317">
       <c r="A317" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>1</v>
@@ -3935,7 +3932,7 @@
     </row>
     <row r="318">
       <c r="A318" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>1</v>
@@ -3943,7 +3940,7 @@
     </row>
     <row r="319">
       <c r="A319" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>1</v>
@@ -3951,119 +3948,119 @@
     </row>
     <row r="320">
       <c r="A320" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B320" s="5">
+        <v>318</v>
+      </c>
+      <c r="B320" s="6">
         <v>12.28012081410357</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B321" s="5">
+        <v>319</v>
+      </c>
+      <c r="B321" s="6">
         <v>9.485409227229336</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B322" s="5">
+        <v>320</v>
+      </c>
+      <c r="B322" s="6">
         <v>14.168378450405877</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="B323" s="5">
+        <v>321</v>
+      </c>
+      <c r="B323" s="6">
         <v>0.5125845143883176</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B324" s="6">
+        <v>322</v>
+      </c>
+      <c r="B324" s="7">
         <v>0.1</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="B325" s="5">
+        <v>323</v>
+      </c>
+      <c r="B325" s="6">
         <v>1.9597979467004172</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="B326" s="5">
+        <v>324</v>
+      </c>
+      <c r="B326" s="6">
         <v>0.10372450796720344</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B327" s="5">
+        <v>325</v>
+      </c>
+      <c r="B327" s="6">
         <v>18.56310220344689</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B328" s="5">
+        <v>326</v>
+      </c>
+      <c r="B328" s="6">
         <v>0.42512088214230054</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B329" s="5">
+        <v>327</v>
+      </c>
+      <c r="B329" s="6">
         <v>7.174404538956834</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B330" s="5">
+        <v>328</v>
+      </c>
+      <c r="B330" s="6">
         <v>2.127917232997722</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B331" s="5">
+        <v>329</v>
+      </c>
+      <c r="B331" s="6">
         <v>7.0228275051137175</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B332" s="5">
+        <v>330</v>
+      </c>
+      <c r="B332" s="6">
         <v>26.139556557297244</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B333" s="6">
+        <v>331</v>
+      </c>
+      <c r="B333" s="7">
         <v>0.1</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>1</v>
@@ -4071,7 +4068,7 @@
     </row>
     <row r="335">
       <c r="A335" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>1</v>
@@ -4079,7 +4076,7 @@
     </row>
     <row r="336">
       <c r="A336" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>1</v>
@@ -4087,7 +4084,7 @@
     </row>
     <row r="337">
       <c r="A337" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>1</v>
@@ -4095,7 +4092,7 @@
     </row>
     <row r="338">
       <c r="A338" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>1</v>
@@ -4103,7 +4100,7 @@
     </row>
     <row r="339">
       <c r="A339" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>1</v>
@@ -4111,7 +4108,7 @@
     </row>
     <row r="340">
       <c r="A340" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>1</v>
@@ -4119,7 +4116,7 @@
     </row>
     <row r="341">
       <c r="A341" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>1</v>
@@ -4127,7 +4124,7 @@
     </row>
     <row r="342">
       <c r="A342" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>1</v>
@@ -4135,7 +4132,7 @@
     </row>
     <row r="343">
       <c r="A343" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>1</v>
@@ -4143,7 +4140,7 @@
     </row>
     <row r="344">
       <c r="A344" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>1</v>
@@ -4151,7 +4148,7 @@
     </row>
     <row r="345">
       <c r="A345" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>1</v>
@@ -4159,7 +4156,7 @@
     </row>
     <row r="346">
       <c r="A346" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>1</v>
@@ -4167,7 +4164,7 @@
     </row>
     <row r="347">
       <c r="A347" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>1</v>
@@ -4175,7 +4172,7 @@
     </row>
     <row r="348">
       <c r="A348" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>1</v>
@@ -4183,7 +4180,7 @@
     </row>
     <row r="349">
       <c r="A349" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>1</v>
@@ -4191,7 +4188,7 @@
     </row>
     <row r="350">
       <c r="A350" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>1</v>
@@ -4199,7 +4196,7 @@
     </row>
     <row r="351">
       <c r="A351" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>1</v>
@@ -4207,7 +4204,7 @@
     </row>
     <row r="352">
       <c r="A352" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>1</v>
@@ -4215,7 +4212,7 @@
     </row>
     <row r="353">
       <c r="A353" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>1</v>
@@ -4223,7 +4220,7 @@
     </row>
     <row r="354">
       <c r="A354" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>1</v>
@@ -4231,7 +4228,7 @@
     </row>
     <row r="355">
       <c r="A355" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>1</v>
@@ -4239,7 +4236,7 @@
     </row>
     <row r="356">
       <c r="A356" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>1</v>
@@ -4247,7 +4244,7 @@
     </row>
     <row r="357">
       <c r="A357" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>1</v>
@@ -4255,7 +4252,7 @@
     </row>
     <row r="358">
       <c r="A358" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>1</v>
@@ -4263,7 +4260,7 @@
     </row>
     <row r="359">
       <c r="A359" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>1</v>
@@ -4271,7 +4268,7 @@
     </row>
     <row r="360">
       <c r="A360" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>1</v>
@@ -4279,7 +4276,7 @@
     </row>
     <row r="361">
       <c r="A361" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>1</v>
@@ -4287,7 +4284,7 @@
     </row>
     <row r="362">
       <c r="A362" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>1</v>
@@ -4295,7 +4292,7 @@
     </row>
     <row r="363">
       <c r="A363" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>1</v>
@@ -4303,7 +4300,7 @@
     </row>
     <row r="364">
       <c r="A364" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>1</v>
@@ -4311,7 +4308,7 @@
     </row>
     <row r="365">
       <c r="A365" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>1</v>

--- a/data/winchance.xlsx
+++ b/data/winchance.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="365">
   <si>
     <t>Saint Louis Billikens</t>
   </si>
@@ -154,63 +154,63 @@
     <t>UAB Blazers</t>
   </si>
   <si>
+    <t>Tulane Green Wave</t>
+  </si>
+  <si>
+    <t>Florida Atlantic Owls</t>
+  </si>
+  <si>
+    <t>Memphis Tigers</t>
+  </si>
+  <si>
+    <t>North Texas Mean Green</t>
+  </si>
+  <si>
+    <t>Temple Owls</t>
+  </si>
+  <si>
+    <t>East Carolina Pirates</t>
+  </si>
+  <si>
+    <t>Rice Owls</t>
+  </si>
+  <si>
+    <t>UTSA Roadrunners</t>
+  </si>
+  <si>
+    <t>Illinois Fighting Illini</t>
+  </si>
+  <si>
+    <t>Central Arkansas Bears</t>
+  </si>
+  <si>
     <t>Austin Peay Governors</t>
   </si>
   <si>
-    <t>Tulane Green Wave</t>
-  </si>
-  <si>
-    <t>Florida Atlantic Owls</t>
-  </si>
-  <si>
-    <t>Memphis Tigers</t>
-  </si>
-  <si>
-    <t>North Texas Mean Green</t>
-  </si>
-  <si>
-    <t>Temple Owls</t>
-  </si>
-  <si>
-    <t>East Carolina Pirates</t>
-  </si>
-  <si>
-    <t>Rice Owls</t>
-  </si>
-  <si>
-    <t>UTSA Roadrunners</t>
-  </si>
-  <si>
-    <t>Illinois Fighting Illini</t>
-  </si>
-  <si>
-    <t>Central Arkansas Bears</t>
+    <t>Queens University Royals</t>
   </si>
   <si>
     <t>Lipscomb Bisons</t>
   </si>
   <si>
-    <t>Queens University Royals</t>
-  </si>
-  <si>
     <t>Bellarmine Knights</t>
   </si>
   <si>
+    <t>West Georgia Wolves</t>
+  </si>
+  <si>
     <t>Florida Gulf Coast Eagles</t>
   </si>
   <si>
+    <t>Jacksonville Dolphins</t>
+  </si>
+  <si>
     <t>Eastern Kentucky Colonels</t>
   </si>
   <si>
     <t>Stetson Hatters</t>
   </si>
   <si>
-    <t>West Georgia Wolves</t>
-  </si>
-  <si>
-    <t>Jacksonville Dolphins</t>
-  </si>
-  <si>
     <t>North Alabama Lions</t>
   </si>
   <si>
@@ -220,69 +220,69 @@
     <t>Michigan Wolverines</t>
   </si>
   <si>
+    <t>Michigan State Spartans</t>
+  </si>
+  <si>
+    <t>Purdue Boilermakers</t>
+  </si>
+  <si>
+    <t>Nebraska Cornhuskers</t>
+  </si>
+  <si>
+    <t>Wisconsin Badgers</t>
+  </si>
+  <si>
+    <t>Ohio State Buckeyes</t>
+  </si>
+  <si>
+    <t>Iowa Hawkeyes</t>
+  </si>
+  <si>
+    <t>UCLA Bruins</t>
+  </si>
+  <si>
+    <t>Minnesota Golden Gophers</t>
+  </si>
+  <si>
+    <t>Indiana Hoosiers</t>
+  </si>
+  <si>
+    <t>Washington Huskies</t>
+  </si>
+  <si>
+    <t>USC Trojans</t>
+  </si>
+  <si>
+    <t>Northwestern Wildcats</t>
+  </si>
+  <si>
+    <t>Maryland Terrapins</t>
+  </si>
+  <si>
+    <t>Oregon Ducks</t>
+  </si>
+  <si>
+    <t>Rutgers Scarlet Knights</t>
+  </si>
+  <si>
+    <t>Penn State Nittany Lions</t>
+  </si>
+  <si>
+    <t>Texas Tech Red Raiders</t>
+  </si>
+  <si>
+    <t>Houston Cougars</t>
+  </si>
+  <si>
+    <t>Iowa State Cyclones</t>
+  </si>
+  <si>
+    <t>Kansas Jayhawks</t>
+  </si>
+  <si>
     <t>Arizona Wildcats</t>
   </si>
   <si>
-    <t>Michigan State Spartans</t>
-  </si>
-  <si>
-    <t>Purdue Boilermakers</t>
-  </si>
-  <si>
-    <t>Nebraska Cornhuskers</t>
-  </si>
-  <si>
-    <t>Wisconsin Badgers</t>
-  </si>
-  <si>
-    <t>Ohio State Buckeyes</t>
-  </si>
-  <si>
-    <t>Iowa Hawkeyes</t>
-  </si>
-  <si>
-    <t>UCLA Bruins</t>
-  </si>
-  <si>
-    <t>Minnesota Golden Gophers</t>
-  </si>
-  <si>
-    <t>Indiana Hoosiers</t>
-  </si>
-  <si>
-    <t>Washington Huskies</t>
-  </si>
-  <si>
-    <t>USC Trojans</t>
-  </si>
-  <si>
-    <t>Northwestern Wildcats</t>
-  </si>
-  <si>
-    <t>Maryland Terrapins</t>
-  </si>
-  <si>
-    <t>Oregon Ducks</t>
-  </si>
-  <si>
-    <t>Rutgers Scarlet Knights</t>
-  </si>
-  <si>
-    <t>Penn State Nittany Lions</t>
-  </si>
-  <si>
-    <t>Texas Tech Red Raiders</t>
-  </si>
-  <si>
-    <t>Houston Cougars</t>
-  </si>
-  <si>
-    <t>Iowa State Cyclones</t>
-  </si>
-  <si>
-    <t>Kansas Jayhawks</t>
-  </si>
-  <si>
     <t>Cincinnati Bearcats</t>
   </si>
   <si>
@@ -370,45 +370,45 @@
     <t>Idaho Vandals</t>
   </si>
   <si>
+    <t>Idaho State Bengals</t>
+  </si>
+  <si>
+    <t>Sacramento State Hornets</t>
+  </si>
+  <si>
+    <t>Northern Arizona Lumberjacks</t>
+  </si>
+  <si>
+    <t>High Point Panthers</t>
+  </si>
+  <si>
+    <t>Winthrop Eagles</t>
+  </si>
+  <si>
+    <t>Radford Highlanders</t>
+  </si>
+  <si>
+    <t>Longwood Lancers</t>
+  </si>
+  <si>
     <t>Charleston Southern Buccaneers</t>
   </si>
   <si>
-    <t>Idaho State Bengals</t>
-  </si>
-  <si>
-    <t>Sacramento State Hornets</t>
-  </si>
-  <si>
-    <t>Northern Arizona Lumberjacks</t>
-  </si>
-  <si>
-    <t>High Point Panthers</t>
-  </si>
-  <si>
-    <t>Winthrop Eagles</t>
+    <t>UNC Asheville Bulldogs</t>
+  </si>
+  <si>
+    <t>Presbyterian Blue Hose</t>
+  </si>
+  <si>
+    <t>South Carolina Upstate Spartans</t>
+  </si>
+  <si>
+    <t>Gardner-Webb Runnin' Bulldogs</t>
   </si>
   <si>
     <t>Cal Poly Mustangs</t>
   </si>
   <si>
-    <t>Longwood Lancers</t>
-  </si>
-  <si>
-    <t>Radford Highlanders</t>
-  </si>
-  <si>
-    <t>UNC Asheville Bulldogs</t>
-  </si>
-  <si>
-    <t>Presbyterian Blue Hose</t>
-  </si>
-  <si>
-    <t>South Carolina Upstate Spartans</t>
-  </si>
-  <si>
-    <t>Gardner-Webb Runnin' Bulldogs</t>
-  </si>
-  <si>
     <t>UC Irvine Anteaters</t>
   </si>
   <si>
@@ -751,55 +751,58 @@
     <t>Central Connecticut Blue Devils</t>
   </si>
   <si>
+    <t>Wagner Seahawks</t>
+  </si>
+  <si>
+    <t>Le Moyne Dolphins</t>
+  </si>
+  <si>
+    <t>Stonehill Skyhawks</t>
+  </si>
+  <si>
+    <t>Fairleigh Dickinson Knights</t>
+  </si>
+  <si>
+    <t>Chicago State Cougars</t>
+  </si>
+  <si>
+    <t>Saint Francis Red Flash</t>
+  </si>
+  <si>
     <t>New Haven Chargers</t>
   </si>
   <si>
-    <t>Le Moyne Dolphins</t>
-  </si>
-  <si>
-    <t>Fairleigh Dickinson Knights</t>
-  </si>
-  <si>
-    <t>Chicago State Cougars</t>
-  </si>
-  <si>
-    <t>Saint Francis Red Flash</t>
+    <t>Tennessee State Tigers</t>
   </si>
   <si>
     <t>Southeast Missouri State Redhawks</t>
   </si>
   <si>
-    <t>Tennessee State Tigers</t>
-  </si>
-  <si>
     <t>Morehead State Eagles</t>
   </si>
   <si>
+    <t>UT Martin Skyhawks</t>
+  </si>
+  <si>
     <t>SIU Edwardsville Cougars</t>
   </si>
   <si>
     <t>Lindenwood Lions</t>
   </si>
   <si>
+    <t>Little Rock Trojans</t>
+  </si>
+  <si>
+    <t>Eastern Illinois Panthers</t>
+  </si>
+  <si>
     <t>Tennessee Tech Golden Eagles</t>
   </si>
   <si>
-    <t>Little Rock Trojans</t>
-  </si>
-  <si>
-    <t>Wagner Seahawks</t>
-  </si>
-  <si>
-    <t>Eastern Illinois Panthers</t>
-  </si>
-  <si>
-    <t>Stonehill Skyhawks</t>
-  </si>
-  <si>
     <t>Southern Indiana Screaming Eagles</t>
   </si>
   <si>
-    <t>UT Martin Skyhawks</t>
+    <t>Western Illinois Leathernecks</t>
   </si>
   <si>
     <t>Navy Midshipmen</t>
@@ -937,34 +940,37 @@
     <t>SE Louisiana Lions</t>
   </si>
   <si>
+    <t>UT Rio Grande Valley Vaqueros</t>
+  </si>
+  <si>
+    <t>Texas A&amp;M-Corpus Christi Islanders</t>
+  </si>
+  <si>
+    <t>St. Thomas-Minnesota Tommies</t>
+  </si>
+  <si>
     <t>North Dakota State Bison</t>
   </si>
   <si>
-    <t>UT Rio Grande Valley Vaqueros</t>
+    <t>Denver Pioneers</t>
+  </si>
+  <si>
+    <t>South Dakota Coyotes</t>
   </si>
   <si>
     <t>Omaha Mavericks</t>
   </si>
   <si>
-    <t>Texas A&amp;M-Corpus Christi Islanders</t>
-  </si>
-  <si>
-    <t>Denver Pioneers</t>
+    <t>South Dakota State Jackrabbits</t>
   </si>
   <si>
     <t>North Dakota Fighting Hawks</t>
   </si>
   <si>
-    <t>South Dakota Coyotes</t>
-  </si>
-  <si>
     <t>Oral Roberts Golden Eagles</t>
   </si>
   <si>
     <t>Kansas City Roos</t>
-  </si>
-  <si>
-    <t>St. Thomas-Minnesota Tommies</t>
   </si>
   <si>
     <t>App State Mountaineers</t>
@@ -1141,7 +1147,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1151,14 +1157,23 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -1382,6 +1397,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="27.75"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -1827,96 +1845,96 @@
       <c r="A56" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>1</v>
+      <c r="B56" s="3">
+        <v>31.98419516</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>1</v>
+      <c r="B57" s="3">
+        <v>22.74135788</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>1</v>
+      <c r="B58" s="3">
+        <v>16.12566168</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>1</v>
+      <c r="B59" s="3">
+        <v>14.20667498</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>1</v>
+      <c r="B60" s="3">
+        <v>3.305748873</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>1</v>
+      <c r="B61" s="3">
+        <v>3.04365461</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>1</v>
+      <c r="B62" s="3">
+        <v>2.652815823</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>1</v>
+      <c r="B63" s="3">
+        <v>1.711529894</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>1</v>
+      <c r="B64" s="3">
+        <v>1.712398877</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>1</v>
+      <c r="B65" s="3">
+        <v>1.533658369</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>1</v>
+      <c r="B66" s="3">
+        <v>0.5264640863</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>1</v>
+      <c r="B67" s="3">
+        <v>0.4558397652</v>
       </c>
     </row>
     <row r="68">
@@ -2355,72 +2373,72 @@
       <c r="A122" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>1</v>
+      <c r="B122" s="4">
+        <v>54.24614187</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>1</v>
+      <c r="B123" s="4">
+        <v>19.83092072</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>1</v>
+      <c r="B124" s="4">
+        <v>6.783712401</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>1</v>
+      <c r="B125" s="4">
+        <v>6.295144394</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>1</v>
+      <c r="B126" s="4">
+        <v>4.613752077</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>1</v>
+      <c r="B127" s="4">
+        <v>4.036612636</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>1</v>
+      <c r="B128" s="4">
+        <v>3.008769125</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>1</v>
+      <c r="B129" s="4">
+        <v>1.165355776</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>1</v>
+      <c r="B130" s="4">
+        <v>0.0195909984</v>
       </c>
     </row>
     <row r="131">
@@ -2715,100 +2733,100 @@
       <c r="A167" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B167" s="3">
+      <c r="B167" s="5">
         <v>33.39</v>
       </c>
-      <c r="C167" s="4"/>
+      <c r="C167" s="6"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B168" s="3">
+      <c r="B168" s="5">
         <v>23.62</v>
       </c>
-      <c r="C168" s="4"/>
+      <c r="C168" s="6"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B169" s="3">
+      <c r="B169" s="5">
         <v>8.0</v>
       </c>
-      <c r="C169" s="4"/>
+      <c r="C169" s="6"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B170" s="3">
+      <c r="B170" s="5">
         <v>15.53</v>
       </c>
-      <c r="C170" s="4"/>
+      <c r="C170" s="6"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B171" s="3">
+      <c r="B171" s="5">
         <v>5.09</v>
       </c>
-      <c r="C171" s="4"/>
+      <c r="C171" s="6"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B172" s="3">
+      <c r="B172" s="5">
         <v>4.33</v>
       </c>
-      <c r="C172" s="4"/>
+      <c r="C172" s="6"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B173" s="3">
+      <c r="B173" s="5">
         <v>3.3000000000000003</v>
       </c>
-      <c r="C173" s="4"/>
+      <c r="C173" s="6"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B174" s="3">
+      <c r="B174" s="5">
         <v>3.0300000000000002</v>
       </c>
-      <c r="C174" s="4"/>
+      <c r="C174" s="6"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B175" s="3">
+      <c r="B175" s="5">
         <v>2.53</v>
       </c>
-      <c r="C175" s="4"/>
+      <c r="C175" s="6"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B176" s="3">
+      <c r="B176" s="5">
         <v>1.17</v>
       </c>
-      <c r="C176" s="4"/>
+      <c r="C176" s="6"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B177" s="3">
+      <c r="B177" s="5">
         <v>0.0</v>
       </c>
-      <c r="C177" s="4"/>
+      <c r="C177" s="6"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="s">
@@ -3334,248 +3352,248 @@
       <c r="A243" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B243" s="2" t="s">
-        <v>1</v>
+      <c r="B243" s="3">
+        <v>38.47109135</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B244" s="2" t="s">
-        <v>1</v>
+      <c r="B244" s="3">
+        <v>15.65015363</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B245" s="2" t="s">
-        <v>1</v>
+      <c r="B245" s="3">
+        <v>11.44057477</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B246" s="2" t="s">
-        <v>1</v>
+      <c r="B246" s="3">
+        <v>9.169416188</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B247" s="2" t="s">
-        <v>1</v>
+      <c r="B247" s="3">
+        <v>11.03678883</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B248" s="2" t="s">
-        <v>1</v>
+      <c r="B248" s="3">
+        <v>5.414355864</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B249" s="2" t="s">
-        <v>1</v>
+      <c r="B249" s="3">
+        <v>4.974029713</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B250" s="2" t="s">
-        <v>1</v>
+      <c r="B250" s="3">
+        <v>3.843589654</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B251" s="2" t="s">
-        <v>1</v>
+      <c r="B251" s="3">
+        <v>0.0</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B252" s="2" t="s">
-        <v>1</v>
+      <c r="B252" s="3">
+        <v>0.0</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B253" s="2" t="s">
-        <v>1</v>
+      <c r="B253" s="3">
+        <v>36.64645925</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B254" s="2" t="s">
-        <v>1</v>
+      <c r="B254" s="3">
+        <v>17.89261716</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B255" s="2" t="s">
-        <v>1</v>
+      <c r="B255" s="3">
+        <v>22.25759702</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B256" s="2" t="s">
-        <v>1</v>
+      <c r="B256" s="3">
+        <v>11.14915126</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B257" s="2" t="s">
-        <v>1</v>
+      <c r="B257" s="3">
+        <v>6.922890455</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B258" s="2" t="s">
-        <v>1</v>
+      <c r="B258" s="3">
+        <v>2.390070708</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B259" s="2" t="s">
-        <v>1</v>
+      <c r="B259" s="3">
+        <v>1.985212</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B260" s="2" t="s">
-        <v>1</v>
+      <c r="B260" s="3">
+        <v>0.7560021529</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B261" s="2" t="s">
-        <v>1</v>
+      <c r="B261" s="3">
+        <v>0.0</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B262" s="2" t="s">
-        <v>1</v>
+      <c r="B262" s="3">
+        <v>0.0</v>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="s">
+      <c r="A263" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="B263" s="5">
-        <v>56.23783103</v>
+      <c r="B263" s="3">
+        <v>0.0</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B264" s="5">
-        <v>11.15277519</v>
+      <c r="B264" s="3">
+        <v>56.23783103</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B265" s="5">
-        <v>8.851240114</v>
+      <c r="B265" s="3">
+        <v>11.15277519</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B266" s="5">
-        <v>8.743822284</v>
+      <c r="B266" s="3">
+        <v>8.851240114</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B267" s="5">
-        <v>5.277871477</v>
+      <c r="B267" s="3">
+        <v>8.743822284</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B268" s="5">
-        <v>4.535970317</v>
+      <c r="B268" s="3">
+        <v>5.277871477</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B269" s="5">
-        <v>2.521686364</v>
+      <c r="B269" s="3">
+        <v>4.535970317</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B270" s="5">
-        <v>1.019683406</v>
+      <c r="B270" s="3">
+        <v>2.521686364</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B271" s="5">
-        <v>0.8704373828</v>
+      <c r="B271" s="3">
+        <v>1.019683406</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B272" s="5">
-        <v>0.788682435</v>
+      <c r="B272" s="3">
+        <v>0.8704373828</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B273" s="2" t="s">
-        <v>1</v>
+      <c r="B273" s="3">
+        <v>0.788682435</v>
       </c>
     </row>
     <row r="274">
@@ -3620,7 +3638,7 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>1</v>
@@ -3628,7 +3646,7 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>1</v>
@@ -3684,7 +3702,7 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>1</v>
@@ -3692,7 +3710,7 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>1</v>
@@ -3894,184 +3912,184 @@
       <c r="A313" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B313" s="2" t="s">
-        <v>1</v>
+      <c r="B313" s="3">
+        <v>38.03123878</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B314" s="2" t="s">
-        <v>1</v>
+      <c r="B314" s="3">
+        <v>33.11349697</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B315" s="2" t="s">
-        <v>1</v>
+      <c r="B315" s="3">
+        <v>6.317888376</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B316" s="2" t="s">
-        <v>1</v>
+      <c r="B316" s="3">
+        <v>5.813643488</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B317" s="2" t="s">
-        <v>1</v>
+      <c r="B317" s="3">
+        <v>5.672462091</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B318" s="2" t="s">
-        <v>1</v>
+      <c r="B318" s="3">
+        <v>5.35137117</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B319" s="2" t="s">
-        <v>1</v>
+      <c r="B319" s="3">
+        <v>4.106878199</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B320" s="6">
-        <v>12.28012081410357</v>
+      <c r="B320" s="3">
+        <v>1.53464943</v>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="s">
+      <c r="A321" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="B321" s="6">
-        <v>9.485409227229336</v>
+      <c r="B321" s="3">
+        <v>0.05837149399</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B322" s="6">
-        <v>14.168378450405877</v>
+      <c r="B322" s="9">
+        <v>12.28012081410357</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B323" s="6">
-        <v>0.5125845143883176</v>
+      <c r="B323" s="9">
+        <v>9.485409227229336</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B324" s="7">
-        <v>0.1</v>
+      <c r="B324" s="9">
+        <v>14.168378450405877</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B325" s="6">
-        <v>1.9597979467004172</v>
+      <c r="B325" s="9">
+        <v>0.5125845143883176</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B326" s="6">
-        <v>0.10372450796720344</v>
+      <c r="B326" s="10">
+        <v>0.1</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B327" s="6">
-        <v>18.56310220344689</v>
+      <c r="B327" s="9">
+        <v>1.9597979467004172</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B328" s="6">
-        <v>0.42512088214230054</v>
+      <c r="B328" s="9">
+        <v>0.10372450796720344</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B329" s="6">
-        <v>7.174404538956834</v>
+      <c r="B329" s="9">
+        <v>18.56310220344689</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B330" s="6">
-        <v>2.127917232997722</v>
+      <c r="B330" s="9">
+        <v>0.42512088214230054</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B331" s="6">
-        <v>7.0228275051137175</v>
+      <c r="B331" s="9">
+        <v>7.174404538956834</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B332" s="6">
-        <v>26.139556557297244</v>
+      <c r="B332" s="9">
+        <v>2.127917232997722</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B333" s="7">
-        <v>0.1</v>
+      <c r="B333" s="9">
+        <v>7.0228275051137175</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B334" s="2" t="s">
-        <v>1</v>
+      <c r="B334" s="9">
+        <v>26.139556557297244</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B335" s="2" t="s">
-        <v>1</v>
+      <c r="B335" s="10">
+        <v>0.1001</v>
       </c>
     </row>
     <row r="336">
@@ -4132,7 +4150,7 @@
     </row>
     <row r="343">
       <c r="A343" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>1</v>
@@ -4140,7 +4158,7 @@
     </row>
     <row r="344">
       <c r="A344" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>1</v>
@@ -4148,7 +4166,7 @@
     </row>
     <row r="345">
       <c r="A345" s="1" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>1</v>
@@ -4311,6 +4329,22 @@
         <v>362</v>
       </c>
       <c r="B365" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B367" s="2" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/winchance.xlsx
+++ b/data/winchance.xlsx
@@ -1164,19 +1164,19 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
@@ -2734,7 +2734,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="5">
-        <v>33.39</v>
+        <v>32.5135119</v>
       </c>
       <c r="C167" s="6"/>
     </row>
@@ -2743,7 +2743,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="5">
-        <v>23.62</v>
+        <v>22.43244549</v>
       </c>
       <c r="C168" s="6"/>
     </row>
@@ -2752,7 +2752,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="5">
-        <v>8.0</v>
+        <v>14.43691924</v>
       </c>
       <c r="C169" s="6"/>
     </row>
@@ -2761,7 +2761,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="5">
-        <v>15.53</v>
+        <v>15.12337369</v>
       </c>
       <c r="C170" s="6"/>
     </row>
@@ -2770,7 +2770,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="5">
-        <v>5.09</v>
+        <v>4.808842126</v>
       </c>
       <c r="C171" s="6"/>
     </row>
@@ -2779,7 +2779,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="5">
-        <v>4.33</v>
+        <v>4.088747844</v>
       </c>
       <c r="C172" s="6"/>
     </row>
@@ -2788,7 +2788,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="5">
-        <v>3.3000000000000003</v>
+        <v>3.114263938</v>
       </c>
       <c r="C173" s="6"/>
     </row>
@@ -2797,7 +2797,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="5">
-        <v>3.0300000000000002</v>
+        <v>0.0</v>
       </c>
       <c r="C174" s="6"/>
     </row>
@@ -2806,7 +2806,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="5">
-        <v>2.53</v>
+        <v>2.380674099</v>
       </c>
       <c r="C175" s="6"/>
     </row>
@@ -2815,7 +2815,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="5">
-        <v>1.17</v>
+        <v>1.101221659</v>
       </c>
       <c r="C176" s="6"/>
     </row>
@@ -3496,7 +3496,7 @@
       <c r="A261" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B261" s="3">
+      <c r="B261" s="7">
         <v>0.0</v>
       </c>
     </row>
@@ -3504,15 +3504,15 @@
       <c r="A262" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B262" s="3">
+      <c r="B262" s="7">
         <v>0.0</v>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="7" t="s">
+      <c r="A263" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="B263" s="3">
+      <c r="B263" s="7">
         <v>0.0</v>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="3">
-        <v>56.23783103</v>
+        <v>55.72156962</v>
       </c>
     </row>
     <row r="265">
@@ -3529,7 +3529,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="3">
-        <v>11.15277519</v>
+        <v>11.18863601</v>
       </c>
     </row>
     <row r="266">
@@ -3537,7 +3537,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="3">
-        <v>8.851240114</v>
+        <v>8.879700538</v>
       </c>
     </row>
     <row r="267">
@@ -3545,7 +3545,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="3">
-        <v>8.743822284</v>
+        <v>9.63310506</v>
       </c>
     </row>
     <row r="268">
@@ -3553,7 +3553,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="3">
-        <v>5.277871477</v>
+        <v>5.294842032</v>
       </c>
     </row>
     <row r="269">
@@ -3561,15 +3561,15 @@
         <v>269</v>
       </c>
       <c r="B269" s="3">
-        <v>4.535970317</v>
+        <v>4.550555351</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B270" s="3">
-        <v>2.521686364</v>
+      <c r="B270" s="7">
+        <v>0.0</v>
       </c>
     </row>
     <row r="271">
@@ -3577,15 +3577,15 @@
         <v>271</v>
       </c>
       <c r="B271" s="3">
-        <v>1.019683406</v>
+        <v>2.661471069</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B272" s="3">
-        <v>0.8704373828</v>
+      <c r="B272" s="7">
+        <v>0.0</v>
       </c>
     </row>
     <row r="273">
@@ -3593,7 +3593,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="3">
-        <v>0.788682435</v>
+        <v>2.070120329</v>
       </c>
     </row>
     <row r="274">
@@ -3973,7 +3973,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="8" t="s">
+      <c r="A321" s="9" t="s">
         <v>319</v>
       </c>
       <c r="B321" s="3">
@@ -3984,32 +3984,32 @@
       <c r="A322" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B322" s="9">
-        <v>12.28012081410357</v>
+      <c r="B322" s="10">
+        <v>12.26346668</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B323" s="9">
-        <v>9.485409227229336</v>
+      <c r="B323" s="10">
+        <v>9.368325575</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B324" s="9">
-        <v>14.168378450405877</v>
+      <c r="B324" s="10">
+        <v>14.14916349</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B325" s="9">
-        <v>0.5125845143883176</v>
+      <c r="B325" s="10">
+        <v>0.5032729887</v>
       </c>
     </row>
     <row r="326">
@@ -4017,71 +4017,71 @@
         <v>324</v>
       </c>
       <c r="B326" s="10">
-        <v>0.1</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B327" s="9">
-        <v>1.9597979467004172</v>
+      <c r="B327" s="10">
+        <v>1.910287628</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B328" s="9">
-        <v>0.10372450796720344</v>
+      <c r="B328" s="10">
+        <v>0.2436865339</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B329" s="9">
-        <v>18.56310220344689</v>
+      <c r="B329" s="10">
+        <v>18.53792718</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B330" s="9">
-        <v>0.42512088214230054</v>
+      <c r="B330" s="10">
+        <v>0.6167541313</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B331" s="9">
-        <v>7.174404538956834</v>
+      <c r="B331" s="10">
+        <v>7.164674711</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B332" s="9">
-        <v>2.127917232997722</v>
+      <c r="B332" s="10">
+        <v>2.125031381</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B333" s="9">
-        <v>7.0228275051137175</v>
+      <c r="B333" s="10">
+        <v>7.013303244</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B334" s="9">
-        <v>26.139556557297244</v>
+      <c r="B334" s="10">
+        <v>26.10410645</v>
       </c>
     </row>
     <row r="335">
@@ -4089,7 +4089,7 @@
         <v>333</v>
       </c>
       <c r="B335" s="10">
-        <v>0.1001</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="336">

--- a/data/winchance.xlsx
+++ b/data/winchance.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="365">
   <si>
     <t>Saint Louis Billikens</t>
   </si>
@@ -574,27 +574,27 @@
     <t>Merrimack Warriors</t>
   </si>
   <si>
+    <t>Siena Saints</t>
+  </si>
+  <si>
+    <t>Saint Peter's Peacocks</t>
+  </si>
+  <si>
     <t>Fairfield Stags</t>
   </si>
   <si>
     <t>Marist Red Foxes</t>
   </si>
   <si>
-    <t>Siena Saints</t>
-  </si>
-  <si>
-    <t>Saint Peter's Peacocks</t>
-  </si>
-  <si>
     <t>Quinnipiac Bobcats</t>
   </si>
   <si>
+    <t>Mount St. Mary's Mountaineers</t>
+  </si>
+  <si>
     <t>Iona Gaels</t>
   </si>
   <si>
-    <t>Mount St. Mary's Mountaineers</t>
-  </si>
-  <si>
     <t>Sacred Heart Pioneers</t>
   </si>
   <si>
@@ -706,42 +706,42 @@
     <t>Utah State Aggies</t>
   </si>
   <si>
+    <t>Wyoming Cowboys</t>
+  </si>
+  <si>
     <t>Belmont Bruins</t>
   </si>
   <si>
+    <t>Illinois State Redbirds</t>
+  </si>
+  <si>
+    <t>Northern Iowa Panthers</t>
+  </si>
+  <si>
+    <t>Bradley Braves</t>
+  </si>
+  <si>
+    <t>Southern Illinois Salukis</t>
+  </si>
+  <si>
     <t>UIC Flames</t>
   </si>
   <si>
-    <t>Bradley Braves</t>
-  </si>
-  <si>
-    <t>Northern Iowa Panthers</t>
-  </si>
-  <si>
-    <t>Illinois State Redbirds</t>
-  </si>
-  <si>
-    <t>Southern Illinois Salukis</t>
-  </si>
-  <si>
-    <t>Wyoming Cowboys</t>
+    <t>Valparaiso Beacons</t>
   </si>
   <si>
     <t>Murray State Racers</t>
   </si>
   <si>
+    <t>Indiana State Sycamores</t>
+  </si>
+  <si>
     <t>Drake Bulldogs</t>
   </si>
   <si>
-    <t>Indiana State Sycamores</t>
-  </si>
-  <si>
     <t>Evansville Purple Aces</t>
   </si>
   <si>
-    <t>Valparaiso Beacons</t>
-  </si>
-  <si>
     <t>Long Island University Sharks</t>
   </si>
   <si>
@@ -1084,10 +1084,10 @@
     <t>Seattle U Redhawks</t>
   </si>
   <si>
+    <t>Oregon State Beavers</t>
+  </si>
+  <si>
     <t>San Francisco Dons</t>
-  </si>
-  <si>
-    <t>Oregon State Beavers</t>
   </si>
   <si>
     <t>Pacific Tigers</t>
@@ -1147,7 +1147,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1160,6 +1160,9 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -1169,9 +1172,6 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
@@ -1179,6 +1179,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -1846,7 +1849,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="3">
-        <v>31.98419516</v>
+        <v>30.5280753</v>
       </c>
     </row>
     <row r="57">
@@ -1854,7 +1857,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="3">
-        <v>22.74135788</v>
+        <v>21.10064441</v>
       </c>
     </row>
     <row r="58">
@@ -1862,7 +1865,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="3">
-        <v>16.12566168</v>
+        <v>15.24683934</v>
       </c>
     </row>
     <row r="59">
@@ -1870,7 +1873,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="3">
-        <v>14.20667498</v>
+        <v>13.35552321</v>
       </c>
     </row>
     <row r="60">
@@ -1878,7 +1881,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="3">
-        <v>3.305748873</v>
+        <v>6.062540633</v>
       </c>
     </row>
     <row r="61">
@@ -1886,7 +1889,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="3">
-        <v>3.04365461</v>
+        <v>5.01367342</v>
       </c>
     </row>
     <row r="62">
@@ -1894,23 +1897,23 @@
         <v>62</v>
       </c>
       <c r="B62" s="3">
-        <v>2.652815823</v>
+        <v>4.652396932</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="3">
-        <v>1.711529894</v>
+      <c r="B63" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="3">
-        <v>1.712398877</v>
+      <c r="B64" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="65">
@@ -1918,23 +1921,23 @@
         <v>65</v>
       </c>
       <c r="B65" s="3">
-        <v>1.533658369</v>
+        <v>4.040306743</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B66" s="3">
-        <v>0.5264640863</v>
+      <c r="B66" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="3">
-        <v>0.4558397652</v>
+      <c r="B67" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="68">
@@ -2373,72 +2376,72 @@
       <c r="A122" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="4">
-        <v>54.24614187</v>
+      <c r="B122" s="5">
+        <v>57.89239586</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B123" s="4">
-        <v>19.83092072</v>
+      <c r="B123" s="5">
+        <v>18.68232487</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B124" s="4">
-        <v>6.783712401</v>
+      <c r="B124" s="5">
+        <v>6.390803569</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B125" s="4">
-        <v>6.295144394</v>
+      <c r="B125" s="5">
+        <v>5.930533149</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B126" s="4">
-        <v>4.613752077</v>
+      <c r="B126" s="5">
+        <v>4.346526135</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B127" s="4">
-        <v>4.036612636</v>
+      <c r="B127" s="5">
+        <v>3.802814287</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B128" s="4">
-        <v>3.008769125</v>
+      <c r="B128" s="5">
+        <v>2.834502898</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B129" s="4">
-        <v>1.165355776</v>
+      <c r="B129" s="5">
+        <v>0.0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B130" s="4">
-        <v>0.0195909984</v>
+      <c r="B130" s="5">
+        <v>0.1200992255</v>
       </c>
     </row>
     <row r="131">
@@ -2733,100 +2736,100 @@
       <c r="A167" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B167" s="5">
-        <v>32.5135119</v>
-      </c>
-      <c r="C167" s="6"/>
+      <c r="B167" s="6">
+        <v>36.814895</v>
+      </c>
+      <c r="C167" s="7"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B168" s="5">
-        <v>22.43244549</v>
-      </c>
-      <c r="C168" s="6"/>
+      <c r="B168" s="6">
+        <v>25.93266414</v>
+      </c>
+      <c r="C168" s="7"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B169" s="5">
-        <v>14.43691924</v>
-      </c>
-      <c r="C169" s="6"/>
+      <c r="B169" s="6">
+        <v>10.28800029</v>
+      </c>
+      <c r="C169" s="7"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B170" s="5">
-        <v>15.12337369</v>
-      </c>
-      <c r="C170" s="6"/>
+      <c r="B170" s="6">
+        <v>19.78300772</v>
+      </c>
+      <c r="C170" s="7"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B171" s="5">
-        <v>4.808842126</v>
-      </c>
-      <c r="C171" s="6"/>
+      <c r="B171" s="6">
+        <v>7.181432838</v>
+      </c>
+      <c r="C171" s="7"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B172" s="5">
-        <v>4.088747844</v>
-      </c>
-      <c r="C172" s="6"/>
+      <c r="B172" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C172" s="7"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B173" s="5">
-        <v>3.114263938</v>
-      </c>
-      <c r="C173" s="6"/>
+      <c r="B173" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C173" s="7"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B174" s="5">
+      <c r="B174" s="6">
         <v>0.0</v>
       </c>
-      <c r="C174" s="6"/>
+      <c r="C174" s="7"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B175" s="5">
-        <v>2.380674099</v>
-      </c>
-      <c r="C175" s="6"/>
+      <c r="B175" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C175" s="7"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B176" s="5">
-        <v>1.101221659</v>
-      </c>
-      <c r="C176" s="6"/>
+      <c r="B176" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C176" s="7"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B177" s="5">
+      <c r="B177" s="6">
         <v>0.0</v>
       </c>
-      <c r="C177" s="6"/>
+      <c r="C177" s="7"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="s">
@@ -2896,80 +2899,80 @@
       <c r="A186" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B186" s="2" t="s">
-        <v>1</v>
+      <c r="B186" s="5">
+        <v>29.69209965</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B187" s="2" t="s">
-        <v>1</v>
+      <c r="B187" s="5">
+        <v>13.26310776</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B188" s="2" t="s">
-        <v>1</v>
+      <c r="B188" s="5">
+        <v>11.87177463</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B189" s="2" t="s">
-        <v>1</v>
+      <c r="B189" s="5">
+        <v>7.015317238</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B190" s="2" t="s">
-        <v>1</v>
+      <c r="B190" s="5">
+        <v>10.42243095</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B191" s="2" t="s">
-        <v>1</v>
+      <c r="B191" s="5">
+        <v>10.28066459</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B192" s="2" t="s">
-        <v>1</v>
+      <c r="B192" s="5">
+        <v>9.345448636</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B193" s="2" t="s">
-        <v>1</v>
+      <c r="B193" s="5">
+        <v>4.549871877</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B194" s="2" t="s">
-        <v>1</v>
+      <c r="B194" s="5">
+        <v>2.776051941</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B195" s="2" t="s">
-        <v>1</v>
+      <c r="B195" s="5">
+        <v>0.7832327334</v>
       </c>
     </row>
     <row r="196">
@@ -3264,88 +3267,88 @@
       <c r="A232" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B232" s="2" t="s">
-        <v>1</v>
+      <c r="B232" s="3">
+        <v>32.93791951</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B233" s="2" t="s">
-        <v>1</v>
+      <c r="B233" s="3">
+        <v>13.28040655</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B234" s="2" t="s">
-        <v>1</v>
+      <c r="B234" s="3">
+        <v>9.767529822</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B235" s="2" t="s">
-        <v>1</v>
+      <c r="B235" s="3">
+        <v>12.66732857</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B236" s="2" t="s">
-        <v>1</v>
+      <c r="B236" s="3">
+        <v>7.662277854</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B237" s="2" t="s">
-        <v>1</v>
+      <c r="B237" s="3">
+        <v>8.819074025</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B238" s="2" t="s">
-        <v>1</v>
+      <c r="B238" s="3">
+        <v>5.682953077</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B239" s="2" t="s">
-        <v>1</v>
+      <c r="B239" s="3">
+        <v>7.079002703</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B240" s="2" t="s">
-        <v>1</v>
+      <c r="B240" s="3">
+        <v>1.161556151</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B241" s="2" t="s">
-        <v>1</v>
+      <c r="B241" s="3">
+        <v>0.8115889437</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B242" s="2" t="s">
-        <v>1</v>
+      <c r="B242" s="3">
+        <v>0.1303627906</v>
       </c>
     </row>
     <row r="243">
@@ -3353,7 +3356,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="3">
-        <v>38.47109135</v>
+        <v>40.54919624</v>
       </c>
     </row>
     <row r="244">
@@ -3361,15 +3364,15 @@
         <v>244</v>
       </c>
       <c r="B244" s="3">
-        <v>15.65015363</v>
+        <v>24.83407063</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B245" s="3">
-        <v>11.44057477</v>
+      <c r="B245" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="246">
@@ -3377,15 +3380,15 @@
         <v>246</v>
       </c>
       <c r="B246" s="3">
-        <v>9.169416188</v>
+        <v>18.08389129</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B247" s="3">
-        <v>11.03678883</v>
+      <c r="B247" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="248">
@@ -3393,30 +3396,30 @@
         <v>248</v>
       </c>
       <c r="B248" s="3">
-        <v>5.414355864</v>
+        <v>16.53284184</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B249" s="3">
-        <v>4.974029713</v>
+      <c r="B249" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B250" s="3">
-        <v>3.843589654</v>
+      <c r="B250" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B251" s="3">
+      <c r="B251" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -3424,7 +3427,7 @@
       <c r="A252" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B252" s="3">
+      <c r="B252" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -3433,7 +3436,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="3">
-        <v>36.64645925</v>
+        <v>36.81130867</v>
       </c>
     </row>
     <row r="254">
@@ -3441,7 +3444,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="3">
-        <v>17.89261716</v>
+        <v>17.45532168</v>
       </c>
     </row>
     <row r="255">
@@ -3449,7 +3452,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="3">
-        <v>22.25759702</v>
+        <v>22.35771997</v>
       </c>
     </row>
     <row r="256">
@@ -3457,15 +3460,15 @@
         <v>256</v>
       </c>
       <c r="B256" s="3">
-        <v>11.14915126</v>
+        <v>14.41212927</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B257" s="3">
-        <v>6.922890455</v>
+      <c r="B257" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="258">
@@ -3473,15 +3476,15 @@
         <v>258</v>
       </c>
       <c r="B258" s="3">
-        <v>2.390070708</v>
+        <v>5.453904295</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B259" s="3">
-        <v>1.985212</v>
+      <c r="B259" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="260">
@@ -3489,14 +3492,14 @@
         <v>260</v>
       </c>
       <c r="B260" s="3">
-        <v>0.7560021529</v>
+        <v>3.509616114</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B261" s="7">
+      <c r="B261" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -3504,7 +3507,7 @@
       <c r="A262" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B262" s="7">
+      <c r="B262" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -3512,7 +3515,7 @@
       <c r="A263" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="B263" s="7">
+      <c r="B263" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -3568,7 +3571,7 @@
       <c r="A270" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B270" s="7">
+      <c r="B270" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -3584,7 +3587,7 @@
       <c r="A272" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B272" s="7">
+      <c r="B272" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -3913,7 +3916,7 @@
         <v>311</v>
       </c>
       <c r="B313" s="3">
-        <v>38.03123878</v>
+        <v>37.89866706</v>
       </c>
     </row>
     <row r="314">
@@ -3921,7 +3924,7 @@
         <v>312</v>
       </c>
       <c r="B314" s="3">
-        <v>33.11349697</v>
+        <v>32.40519309</v>
       </c>
     </row>
     <row r="315">
@@ -3929,7 +3932,7 @@
         <v>313</v>
       </c>
       <c r="B315" s="3">
-        <v>6.317888376</v>
+        <v>6.295865077</v>
       </c>
     </row>
     <row r="316">
@@ -3937,7 +3940,7 @@
         <v>314</v>
       </c>
       <c r="B316" s="3">
-        <v>5.813643488</v>
+        <v>5.793377918</v>
       </c>
     </row>
     <row r="317">
@@ -3945,7 +3948,7 @@
         <v>315</v>
       </c>
       <c r="B317" s="3">
-        <v>5.672462091</v>
+        <v>5.65268866</v>
       </c>
     </row>
     <row r="318">
@@ -3953,7 +3956,7 @@
         <v>316</v>
       </c>
       <c r="B318" s="3">
-        <v>5.35137117</v>
+        <v>5.332717018</v>
       </c>
     </row>
     <row r="319">
@@ -3961,7 +3964,7 @@
         <v>317</v>
       </c>
       <c r="B319" s="3">
-        <v>4.106878199</v>
+        <v>4.09256218</v>
       </c>
     </row>
     <row r="320">
@@ -3969,15 +3972,15 @@
         <v>318</v>
       </c>
       <c r="B320" s="3">
-        <v>1.53464943</v>
+        <v>2.528928997</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="B321" s="3">
-        <v>0.05837149399</v>
+      <c r="B321" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="322">
@@ -3985,7 +3988,7 @@
         <v>320</v>
       </c>
       <c r="B322" s="10">
-        <v>12.26346668</v>
+        <v>12.10952903</v>
       </c>
     </row>
     <row r="323">
@@ -3993,7 +3996,7 @@
         <v>321</v>
       </c>
       <c r="B323" s="10">
-        <v>9.368325575</v>
+        <v>9.177291724</v>
       </c>
     </row>
     <row r="324">
@@ -4001,7 +4004,7 @@
         <v>322</v>
       </c>
       <c r="B324" s="10">
-        <v>14.14916349</v>
+        <v>13.97155556</v>
       </c>
     </row>
     <row r="325">
@@ -4009,14 +4012,14 @@
         <v>323</v>
       </c>
       <c r="B325" s="10">
-        <v>0.5032729887</v>
+        <v>1.274719923</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B326" s="10">
+      <c r="B326" s="11">
         <v>0.0</v>
       </c>
     </row>
@@ -4025,15 +4028,15 @@
         <v>325</v>
       </c>
       <c r="B327" s="10">
-        <v>1.910287628</v>
+        <v>3.605999495</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B328" s="10">
-        <v>0.2436865339</v>
+      <c r="B328" s="11">
+        <v>0.0</v>
       </c>
     </row>
     <row r="329">
@@ -4041,15 +4044,15 @@
         <v>327</v>
       </c>
       <c r="B329" s="10">
-        <v>18.53792718</v>
+        <v>18.30522912</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B330" s="10">
-        <v>0.6167541313</v>
+      <c r="B330" s="11">
+        <v>0.0</v>
       </c>
     </row>
     <row r="331">
@@ -4057,7 +4060,7 @@
         <v>329</v>
       </c>
       <c r="B331" s="10">
-        <v>7.164674711</v>
+        <v>7.074739849</v>
       </c>
     </row>
     <row r="332">
@@ -4065,7 +4068,7 @@
         <v>330</v>
       </c>
       <c r="B332" s="10">
-        <v>2.125031381</v>
+        <v>2.018877463</v>
       </c>
     </row>
     <row r="333">
@@ -4073,7 +4076,7 @@
         <v>331</v>
       </c>
       <c r="B333" s="10">
-        <v>7.013303244</v>
+        <v>6.685624205</v>
       </c>
     </row>
     <row r="334">
@@ -4081,14 +4084,14 @@
         <v>332</v>
       </c>
       <c r="B334" s="10">
-        <v>26.10410645</v>
+        <v>25.77643363</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B335" s="10">
+      <c r="B335" s="11">
         <v>0.0</v>
       </c>
     </row>
@@ -4256,96 +4259,96 @@
       <c r="A356" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B356" s="2" t="s">
-        <v>1</v>
+      <c r="B356" s="3">
+        <v>35.72308781</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B357" s="2" t="s">
-        <v>1</v>
+      <c r="B357" s="3">
+        <v>45.92766961</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B358" s="2" t="s">
-        <v>1</v>
+      <c r="B358" s="3">
+        <v>13.81274125</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B359" s="2" t="s">
-        <v>1</v>
+      <c r="B359" s="3">
+        <v>0.5389927286</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B360" s="2" t="s">
-        <v>1</v>
+      <c r="B360" s="3">
+        <v>2.088397481</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B361" s="2" t="s">
-        <v>1</v>
+      <c r="B361" s="3">
+        <v>0.9928765358</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B362" s="2" t="s">
-        <v>1</v>
+      <c r="B362" s="3">
+        <v>0.366372174</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B363" s="2" t="s">
-        <v>1</v>
+      <c r="B363" s="3">
+        <v>0.3886394336</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B364" s="2" t="s">
-        <v>1</v>
+      <c r="B364" s="3">
+        <v>0.08014343457</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B365" s="2" t="s">
-        <v>1</v>
+      <c r="B365" s="3">
+        <v>0.05383831989</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B366" s="2" t="s">
-        <v>1</v>
+      <c r="B366" s="3">
+        <v>0.006243916315</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B367" s="2" t="s">
-        <v>1</v>
+      <c r="B367" s="3">
+        <v>0.02099730347</v>
       </c>
     </row>
   </sheetData>
